--- a/real_pos.xlsx
+++ b/real_pos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Huynh\pick_and_place\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765AB001-E5CC-4BA7-A578-657DF8FE6171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BAD732-E242-4561-BC4C-A9139B5CB6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20130" yWindow="4245" windowWidth="21600" windowHeight="11235" xr2:uid="{AA6FFCD5-2D5B-4F40-A805-3FDF4A20B841}"/>
+    <workbookView xWindow="-300" yWindow="2805" windowWidth="21600" windowHeight="11235" xr2:uid="{AA6FFCD5-2D5B-4F40-A805-3FDF4A20B841}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
   <si>
     <t>Image pixel</t>
   </si>
@@ -425,10 +425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A9D97A-FAFF-410A-81D2-1F8B34A1035F}">
-  <dimension ref="A6:E17"/>
+  <dimension ref="A6:M17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -437,8 +437,16 @@
         <v>3</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -451,8 +459,20 @@
       <c r="E7" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2347.42</v>
       </c>
@@ -465,8 +485,20 @@
       <c r="E8">
         <v>139.41</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I8">
+        <v>2078.2399999999998</v>
+      </c>
+      <c r="J8">
+        <v>221.76</v>
+      </c>
+      <c r="L8">
+        <v>750.99</v>
+      </c>
+      <c r="M8">
+        <v>109.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2456.06</v>
       </c>
@@ -479,8 +511,20 @@
       <c r="E9">
         <v>57.25</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <v>1585.33</v>
+      </c>
+      <c r="J9">
+        <v>208.66</v>
+      </c>
+      <c r="L9">
+        <v>648.23</v>
+      </c>
+      <c r="M9">
+        <v>109.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2061.79</v>
       </c>
@@ -493,8 +537,20 @@
       <c r="E10">
         <v>36.17</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <v>799.31</v>
+      </c>
+      <c r="J10">
+        <v>555.55999999999995</v>
+      </c>
+      <c r="L10">
+        <v>488.38</v>
+      </c>
+      <c r="M10">
+        <v>34.71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1752.28</v>
       </c>
@@ -507,8 +563,20 @@
       <c r="E11">
         <v>139.03</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <v>861.14</v>
+      </c>
+      <c r="J11">
+        <v>965.58</v>
+      </c>
+      <c r="L11">
+        <v>502.89</v>
+      </c>
+      <c r="M11">
+        <v>-49.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2154.19</v>
       </c>
@@ -520,6 +588,74 @@
       </c>
       <c r="E12">
         <v>97.66</v>
+      </c>
+      <c r="I12">
+        <v>1159.7</v>
+      </c>
+      <c r="J12">
+        <v>958.41</v>
+      </c>
+      <c r="L12">
+        <v>564.24</v>
+      </c>
+      <c r="M12">
+        <v>-45.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I13">
+        <v>1378.74</v>
+      </c>
+      <c r="J13">
+        <v>1618.02</v>
+      </c>
+      <c r="L13">
+        <v>612.51</v>
+      </c>
+      <c r="M13">
+        <v>-180.68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I14">
+        <v>785.82</v>
+      </c>
+      <c r="J14">
+        <v>1638.68</v>
+      </c>
+      <c r="L14">
+        <v>490.08</v>
+      </c>
+      <c r="M14">
+        <v>-187.69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I15">
+        <v>2261.41</v>
+      </c>
+      <c r="J15">
+        <v>943.43</v>
+      </c>
+      <c r="L15">
+        <v>792.44</v>
+      </c>
+      <c r="M15">
+        <v>-38.619999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I16">
+        <v>2180.17</v>
+      </c>
+      <c r="J16">
+        <v>1639.43</v>
+      </c>
+      <c r="L16">
+        <v>778.74</v>
+      </c>
+      <c r="M16">
+        <v>-182.72</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -531,9 +667,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="L6:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
